--- a/04_Figures/F04_association/modules/acute/lm/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/acute/lm/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -488,16 +482,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.838625041418221</v>
+        <v>-19.8028520225925</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0516804722242783</v>
+        <v>-1.55386581495652</v>
       </c>
       <c r="F2" t="n">
-        <v>0.959568974738458</v>
+        <v>0.144215529052036</v>
       </c>
       <c r="G2" t="n">
-        <v>0.959568974738458</v>
+        <v>0.326459012075262</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-25.2722359094128</v>
+        <v>0.199757062345179</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.61703749499538</v>
+        <v>0.0149860037707946</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0213056673559911</v>
+        <v>0.988270898207627</v>
       </c>
       <c r="G3" t="n">
-        <v>0.241821782320226</v>
+        <v>0.988270898207627</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +528,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-17.3961898505838</v>
+        <v>-26.6177305836686</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.63710582102735</v>
+        <v>-2.92164608989415</v>
       </c>
       <c r="F4" t="n">
-        <v>0.12557461106173</v>
+        <v>0.0119028199059526</v>
       </c>
       <c r="G4" t="n">
-        <v>0.319476307722578</v>
+        <v>0.130931018965479</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +551,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.8626584727615</v>
+        <v>21.1042995030596</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.199854731926405</v>
+        <v>1.85137782303695</v>
       </c>
       <c r="F5" t="n">
-        <v>0.844686526173134</v>
+        <v>0.0869597552121412</v>
       </c>
       <c r="G5" t="n">
-        <v>0.955443302463625</v>
+        <v>0.318852435777851</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-10.2947023017504</v>
+        <v>-11.3644654343705</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.76950678464638</v>
+        <v>-0.851605223442449</v>
       </c>
       <c r="F6" t="n">
-        <v>0.455347742460236</v>
+        <v>0.40984698970092</v>
       </c>
       <c r="G6" t="n">
-        <v>0.739940081497883</v>
+        <v>0.500924098523346</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +597,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.19174245560845</v>
+        <v>-0.308303657313051</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.406746432733069</v>
+        <v>-0.0188757842905784</v>
       </c>
       <c r="F7" t="n">
-        <v>0.690811390480505</v>
+        <v>0.98522683131289</v>
       </c>
       <c r="G7" t="n">
-        <v>0.955443302463625</v>
+        <v>0.988270898207627</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +620,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.03753925868059</v>
+        <v>19.9056869143529</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.151447523054352</v>
+        <v>1.87507984846501</v>
       </c>
       <c r="F8" t="n">
-        <v>0.881947663812576</v>
+        <v>0.0834209934074621</v>
       </c>
       <c r="G8" t="n">
-        <v>0.955443302463625</v>
+        <v>0.318852435777851</v>
       </c>
     </row>
     <row r="9">
@@ -649,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>24.0245409403141</v>
+        <v>-17.7718488826961</v>
       </c>
       <c r="E9" t="n">
-        <v>2.16296820277986</v>
+        <v>-1.25235095667709</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0497628853240413</v>
+        <v>0.232503994520837</v>
       </c>
       <c r="G9" t="n">
-        <v>0.241821782320226</v>
+        <v>0.326459012075262</v>
       </c>
     </row>
     <row r="10">
@@ -672,16 +666,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>22.4966427080502</v>
+        <v>-18.3532438737808</v>
       </c>
       <c r="E10" t="n">
-        <v>1.93984720671715</v>
+        <v>-1.34955101505648</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0744067022523772</v>
+        <v>0.200193825071446</v>
       </c>
       <c r="G10" t="n">
-        <v>0.241821782320226</v>
+        <v>0.326459012075262</v>
       </c>
     </row>
     <row r="11">
@@ -695,16 +689,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.67559284067403</v>
+        <v>13.4800945199108</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.269155359189579</v>
+        <v>1.23851213750601</v>
       </c>
       <c r="F11" t="n">
-        <v>0.792034664058781</v>
+        <v>0.237424736054736</v>
       </c>
       <c r="G11" t="n">
-        <v>0.955443302463625</v>
+        <v>0.326459012075262</v>
       </c>
     </row>
     <row r="12">
@@ -718,62 +712,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>17.6051543382665</v>
+        <v>-16.6399803624679</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0121351366343</v>
+        <v>-1.51034068971231</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0654023389109333</v>
+        <v>0.154875433019355</v>
       </c>
       <c r="G12" t="n">
-        <v>0.241821782320226</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>13.0627200078071</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.19543749629191</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.253268067947139</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.4703549833304</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-19.5340646149979</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.54037440010914</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.147450603564267</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.319476307722578</v>
+        <v>0.326459012075262</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -821,21 +769,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-2006.36482310007</v>
+        <v>-1831.1691633791</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.744593976022966</v>
+        <v>-0.7970941051847</v>
       </c>
       <c r="F2" t="n">
-        <v>0.469764241929915</v>
+        <v>0.439712537294184</v>
       </c>
       <c r="G2" t="n">
-        <v>0.740140872905592</v>
+        <v>0.665952473217071</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -844,21 +792,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-2491.87894708524</v>
+        <v>5.81804949862265</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.31060457476489</v>
+        <v>0.00257444871704155</v>
       </c>
       <c r="F3" t="n">
-        <v>0.212673746666978</v>
+        <v>0.997984976330094</v>
       </c>
       <c r="G3" t="n">
-        <v>0.740140872905592</v>
+        <v>0.997984976330094</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -867,21 +815,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-2530.62380882382</v>
+        <v>-2785.03733825886</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.36797310127461</v>
+        <v>-1.52033550208785</v>
       </c>
       <c r="F4" t="n">
-        <v>0.194502279023928</v>
+        <v>0.152370003822515</v>
       </c>
       <c r="G4" t="n">
-        <v>0.740140872905592</v>
+        <v>0.665952473217071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -890,21 +838,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-943.435771695743</v>
+        <v>1518.01172844644</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.390162778133914</v>
+        <v>0.712234288842398</v>
       </c>
       <c r="F5" t="n">
-        <v>0.702733955404376</v>
+        <v>0.488905937254622</v>
       </c>
       <c r="G5" t="n">
-        <v>0.799133444178153</v>
+        <v>0.665952473217071</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -913,21 +861,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-1336.59343884318</v>
+        <v>-1470.74710374095</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.583811098761472</v>
+        <v>-0.64262355913213</v>
       </c>
       <c r="F6" t="n">
-        <v>0.569339133004301</v>
+        <v>0.531639136839486</v>
       </c>
       <c r="G6" t="n">
-        <v>0.740140872905592</v>
+        <v>0.665952473217071</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -936,21 +884,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-741.916206229207</v>
+        <v>-1911.79236314425</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.342210685120395</v>
+        <v>-0.703394296255146</v>
       </c>
       <c r="F7" t="n">
-        <v>0.737661640779834</v>
+        <v>0.494215874548145</v>
       </c>
       <c r="G7" t="n">
-        <v>0.799133444178153</v>
+        <v>0.665952473217071</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -959,21 +907,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-408.673820391173</v>
+        <v>1897.232494672</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.179230915959496</v>
+        <v>0.968354095659915</v>
       </c>
       <c r="F8" t="n">
-        <v>0.860519689624292</v>
+        <v>0.350539085503903</v>
       </c>
       <c r="G8" t="n">
-        <v>0.860519689624292</v>
+        <v>0.665952473217071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -982,21 +930,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>2215.77576485098</v>
+        <v>-1050.19692191316</v>
       </c>
       <c r="E9" t="n">
-        <v>1.05100904827958</v>
+        <v>-0.415064644023429</v>
       </c>
       <c r="F9" t="n">
-        <v>0.312399972076265</v>
+        <v>0.684863056348956</v>
       </c>
       <c r="G9" t="n">
-        <v>0.740140872905592</v>
+        <v>0.753349361983852</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1005,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>1790.85239536808</v>
+        <v>-1508.36320511508</v>
       </c>
       <c r="E10" t="n">
-        <v>0.822723376751907</v>
+        <v>-0.621728063442125</v>
       </c>
       <c r="F10" t="n">
-        <v>0.425499744540527</v>
+        <v>0.544870205359422</v>
       </c>
       <c r="G10" t="n">
-        <v>0.740140872905592</v>
+        <v>0.665952473217071</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1028,21 +976,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>1212.38237789172</v>
+        <v>1789.85514091352</v>
       </c>
       <c r="E11" t="n">
-        <v>0.732003972743726</v>
+        <v>0.948559213049807</v>
       </c>
       <c r="F11" t="n">
-        <v>0.477156080091811</v>
+        <v>0.360145820009674</v>
       </c>
       <c r="G11" t="n">
-        <v>0.740140872905592</v>
+        <v>0.665952473217071</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1051,62 +999,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>2419.42327765293</v>
+        <v>-2287.41502853672</v>
       </c>
       <c r="E12" t="n">
-        <v>1.55031453616218</v>
+        <v>-1.18937144013696</v>
       </c>
       <c r="F12" t="n">
-        <v>0.145061132912024</v>
+        <v>0.255564028487417</v>
       </c>
       <c r="G12" t="n">
-        <v>0.740140872905592</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1728.85729581191</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.913797548450008</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.377460019935997</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.740140872905592</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-1366.45318312596</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.592288242392521</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.563817903539654</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.740140872905592</v>
+        <v>0.665952473217071</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1047,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1154,21 +1056,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-838.083938597969</v>
+        <v>-2150.46198197881</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.328789766337648</v>
+        <v>-1.02116987607147</v>
       </c>
       <c r="F2" t="n">
-        <v>0.747550965190722</v>
+        <v>0.325802273904693</v>
       </c>
       <c r="G2" t="n">
-        <v>0.773711687334684</v>
+        <v>0.608989586674783</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1177,21 +1079,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-2447.28791577614</v>
+        <v>161.7391574732</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.3942263101683</v>
+        <v>0.0769506868209312</v>
       </c>
       <c r="F3" t="n">
-        <v>0.186621415737719</v>
+        <v>0.939834489265089</v>
       </c>
       <c r="G3" t="n">
-        <v>0.665383871972144</v>
+        <v>0.939834489265089</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1200,21 +1102,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-2242.36881606569</v>
+        <v>-2517.64861316185</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.29440353341761</v>
+        <v>-1.47012895869615</v>
       </c>
       <c r="F4" t="n">
-        <v>0.218047104239648</v>
+        <v>0.165311245042876</v>
       </c>
       <c r="G4" t="n">
-        <v>0.665383871972144</v>
+        <v>0.608989586674783</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1223,21 +1125,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-662.060312418</v>
+        <v>1701.26499875653</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.293582210977419</v>
+        <v>0.865705378026609</v>
       </c>
       <c r="F5" t="n">
-        <v>0.773711687334684</v>
+        <v>0.402346044060772</v>
       </c>
       <c r="G5" t="n">
-        <v>0.773711687334684</v>
+        <v>0.608989586674783</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1246,21 +1148,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-1416.43455692461</v>
+        <v>-1535.2195422854</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.66767147520876</v>
+        <v>-0.724061207046354</v>
       </c>
       <c r="F6" t="n">
-        <v>0.516021670527476</v>
+        <v>0.481855882043415</v>
       </c>
       <c r="G6" t="n">
-        <v>0.745364635206355</v>
+        <v>0.608989586674783</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1269,21 +1171,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-693.289573200613</v>
+        <v>-808.696396173346</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.343765865889575</v>
+        <v>-0.315120577357198</v>
       </c>
       <c r="F7" t="n">
-        <v>0.736518787314769</v>
+        <v>0.757671239867265</v>
       </c>
       <c r="G7" t="n">
-        <v>0.773711687334684</v>
+        <v>0.833438363853992</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1292,21 +1194,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-946.018454908838</v>
+        <v>1516.76537516543</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.448881161187959</v>
+        <v>0.824454595607621</v>
       </c>
       <c r="F8" t="n">
-        <v>0.660908848844641</v>
+        <v>0.424550611172814</v>
       </c>
       <c r="G8" t="n">
-        <v>0.773711687334684</v>
+        <v>0.608989586674783</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1315,21 +1217,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>1694.45355912105</v>
+        <v>-1620.70298921829</v>
       </c>
       <c r="E9" t="n">
-        <v>0.85231536639583</v>
+        <v>-0.696692765033034</v>
       </c>
       <c r="F9" t="n">
-        <v>0.409466998136704</v>
+        <v>0.498264207279368</v>
       </c>
       <c r="G9" t="n">
-        <v>0.665383871972144</v>
+        <v>0.608989586674783</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1338,21 +1240,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>1948.94843117427</v>
+        <v>-2085.04022075753</v>
       </c>
       <c r="E10" t="n">
-        <v>0.971837531135743</v>
+        <v>-0.9409011152064</v>
       </c>
       <c r="F10" t="n">
-        <v>0.348867488983709</v>
+        <v>0.363911597815872</v>
       </c>
       <c r="G10" t="n">
-        <v>0.665383871972144</v>
+        <v>0.608989586674783</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1361,21 +1263,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>1468.74620886958</v>
+        <v>1608.65040531608</v>
       </c>
       <c r="E11" t="n">
-        <v>0.967234538373521</v>
+        <v>0.914326695409156</v>
       </c>
       <c r="F11" t="n">
-        <v>0.351077532214417</v>
+        <v>0.377192220238452</v>
       </c>
       <c r="G11" t="n">
-        <v>0.665383871972144</v>
+        <v>0.608989586674783</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1384,62 +1286,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>2211.70774899184</v>
+        <v>-2001.45644527105</v>
       </c>
       <c r="E12" t="n">
-        <v>1.51863125751462</v>
+        <v>-1.11173794396687</v>
       </c>
       <c r="F12" t="n">
-        <v>0.152794758261406</v>
+        <v>0.286388621884417</v>
       </c>
       <c r="G12" t="n">
-        <v>0.665383871972144</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1553.89321443555</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.881004157335413</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.394312263689237</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.665383871972144</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-1864.72804520353</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.882678616207261</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.393439594572929</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.665383871972144</v>
+        <v>0.608989586674783</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1334,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1487,21 +1343,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>2.49861131017988</v>
+        <v>-2.5990843459007</v>
       </c>
       <c r="E2" t="n">
-        <v>0.726527134857524</v>
+        <v>-0.892532889695748</v>
       </c>
       <c r="F2" t="n">
-        <v>0.480393762377316</v>
+        <v>0.388330430768287</v>
       </c>
       <c r="G2" t="n">
-        <v>0.780639863863139</v>
+        <v>0.650724547651384</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1510,21 +1366,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.93245948341149</v>
+        <v>-0.642236812406813</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.68228978686579</v>
+        <v>-0.223307346728736</v>
       </c>
       <c r="F3" t="n">
-        <v>0.116361799496738</v>
+        <v>0.826766984859307</v>
       </c>
       <c r="G3" t="n">
-        <v>0.53281143720766</v>
+        <v>0.909443683345238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1533,21 +1389,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.474181817088328</v>
+        <v>-4.25483212086298</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.188214029077383</v>
+        <v>-1.89656152045229</v>
       </c>
       <c r="F4" t="n">
-        <v>0.853615087965892</v>
+        <v>0.0803268634016934</v>
       </c>
       <c r="G4" t="n">
-        <v>0.986685759009664</v>
+        <v>0.650724547651384</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1556,21 +1412,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.57161918392207</v>
+        <v>3.85070946165034</v>
       </c>
       <c r="E5" t="n">
-        <v>0.184565411533427</v>
+        <v>1.50657416777246</v>
       </c>
       <c r="F5" t="n">
-        <v>0.856418010603111</v>
+        <v>0.155828632631093</v>
       </c>
       <c r="G5" t="n">
-        <v>0.986685759009664</v>
+        <v>0.650724547651384</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1579,21 +1435,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0976852916113394</v>
+        <v>-0.0537277374624849</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0330346972626204</v>
+        <v>-0.0181259885834632</v>
       </c>
       <c r="F6" t="n">
-        <v>0.974148741102882</v>
+        <v>0.985813589718922</v>
       </c>
       <c r="G6" t="n">
-        <v>0.986685759009664</v>
+        <v>0.985813589718922</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1602,21 +1458,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.05296457953113</v>
+        <v>2.55496905702803</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.755388863017387</v>
+        <v>0.738634668056558</v>
       </c>
       <c r="F7" t="n">
-        <v>0.463483052598514</v>
+        <v>0.473254216473734</v>
       </c>
       <c r="G7" t="n">
-        <v>0.780639863863139</v>
+        <v>0.650724547651384</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1625,21 +1481,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0495185349668357</v>
+        <v>2.53908034663988</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0170114975689555</v>
+        <v>1.02013619027183</v>
       </c>
       <c r="F8" t="n">
-        <v>0.986685759009664</v>
+        <v>0.326273949657831</v>
       </c>
       <c r="G8" t="n">
-        <v>0.986685759009664</v>
+        <v>0.650724547651384</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1648,21 +1504,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>3.82809565857467</v>
+        <v>-3.93439191678535</v>
       </c>
       <c r="E9" t="n">
-        <v>1.47751537645069</v>
+        <v>-1.28632050347678</v>
       </c>
       <c r="F9" t="n">
-        <v>0.163351025652262</v>
+        <v>0.220768510946181</v>
       </c>
       <c r="G9" t="n">
-        <v>0.53281143720766</v>
+        <v>0.650724547651384</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1671,21 +1527,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>3.88704135449898</v>
+        <v>-2.74331850310435</v>
       </c>
       <c r="E10" t="n">
-        <v>1.47528073931066</v>
+        <v>-0.90079419099944</v>
       </c>
       <c r="F10" t="n">
-        <v>0.16394198067928</v>
+        <v>0.384082157940709</v>
       </c>
       <c r="G10" t="n">
-        <v>0.53281143720766</v>
+        <v>0.650724547651384</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1694,21 +1550,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.06106184945904</v>
+        <v>1.98591391778875</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.09542961446254</v>
+        <v>0.818574632240305</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00852140585097384</v>
+        <v>0.427779910599933</v>
       </c>
       <c r="G11" t="n">
-        <v>0.11077827606266</v>
+        <v>0.650724547651384</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1717,62 +1573,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.715848736690424</v>
+        <v>-0.742275931801893</v>
       </c>
       <c r="E12" t="n">
-        <v>0.331889453595789</v>
+        <v>-0.288378349313789</v>
       </c>
       <c r="F12" t="n">
-        <v>0.745262723750202</v>
+        <v>0.777603804048202</v>
       </c>
       <c r="G12" t="n">
-        <v>0.986685759009664</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.9692176748319</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.811063925418847</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.431928027296765</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.780639863863139</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-3.52127632681842</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.25020129347444</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.233263013308765</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.60648383460279</v>
+        <v>0.909443683345238</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1621,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1820,21 +1630,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-26.8330817775534</v>
+        <v>-16.0931724773999</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.446050684182747</v>
+        <v>-0.311639165548412</v>
       </c>
       <c r="F2" t="n">
-        <v>0.662899475860843</v>
+        <v>0.760256308912872</v>
       </c>
       <c r="G2" t="n">
-        <v>0.662899475860843</v>
+        <v>0.836281939804159</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1843,21 +1653,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-27.1840440745916</v>
+        <v>48.2552228838552</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.618856811909698</v>
+        <v>1.00626632177205</v>
       </c>
       <c r="F3" t="n">
-        <v>0.546702504222062</v>
+        <v>0.332650869719392</v>
       </c>
       <c r="G3" t="n">
-        <v>0.662899475860843</v>
+        <v>0.779723152054572</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1866,21 +1676,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-36.8458058819689</v>
+        <v>-30.1017933264706</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.869530586855158</v>
+        <v>-0.700126495376226</v>
       </c>
       <c r="F4" t="n">
-        <v>0.400327093224326</v>
+        <v>0.496187460398364</v>
       </c>
       <c r="G4" t="n">
-        <v>0.662899475860843</v>
+        <v>0.779723152054572</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1889,21 +1699,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>52.8190838863637</v>
+        <v>-43.2717202142376</v>
       </c>
       <c r="E5" t="n">
-        <v>1.02480438518952</v>
+        <v>-0.933933155737733</v>
       </c>
       <c r="F5" t="n">
-        <v>0.324147768250156</v>
+        <v>0.367361865998706</v>
       </c>
       <c r="G5" t="n">
-        <v>0.662899475860843</v>
+        <v>0.779723152054572</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1912,21 +1722,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-34.2010777728355</v>
+        <v>-39.6305091154047</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.681214443831772</v>
+        <v>-0.792267082311637</v>
       </c>
       <c r="F6" t="n">
-        <v>0.507689562583105</v>
+        <v>0.442423164250438</v>
       </c>
       <c r="G6" t="n">
-        <v>0.662899475860843</v>
+        <v>0.779723152054572</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1935,21 +1745,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-24.4763810347584</v>
+        <v>-26.8369391519226</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.51535294858459</v>
+        <v>-0.443211929627197</v>
       </c>
       <c r="F7" t="n">
-        <v>0.614957568201561</v>
+        <v>0.664898603588901</v>
       </c>
       <c r="G7" t="n">
-        <v>0.662899475860843</v>
+        <v>0.812653848830879</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1958,21 +1768,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-42.2448212682838</v>
+        <v>-38.7266436624005</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.863703201306791</v>
+        <v>-0.892673523485708</v>
       </c>
       <c r="F8" t="n">
-        <v>0.40340551482017</v>
+        <v>0.388257844561238</v>
       </c>
       <c r="G8" t="n">
-        <v>0.662899475860843</v>
+        <v>0.779723152054572</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1981,21 +1791,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.2807765583228</v>
+        <v>-2.51205188047842</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.855744349792592</v>
+        <v>-0.0447736960681834</v>
       </c>
       <c r="F9" t="n">
-        <v>0.407635478246004</v>
+        <v>0.964968145011922</v>
       </c>
       <c r="G9" t="n">
-        <v>0.662899475860843</v>
+        <v>0.964968145011922</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2004,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-39.5704193352634</v>
+        <v>48.4078550845274</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.825289799590484</v>
+        <v>0.921199796142855</v>
       </c>
       <c r="F10" t="n">
-        <v>0.424093209519591</v>
+        <v>0.373725673117414</v>
       </c>
       <c r="G10" t="n">
-        <v>0.662899475860843</v>
+        <v>0.779723152054572</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2027,21 +1837,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>52.1233403582261</v>
+        <v>23.5387801021564</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5191262228227</v>
+        <v>0.55403966190022</v>
       </c>
       <c r="F11" t="n">
-        <v>0.152671292782657</v>
+        <v>0.588955605819739</v>
       </c>
       <c r="G11" t="n">
-        <v>0.662899475860843</v>
+        <v>0.809813958002142</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2050,62 +1860,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>22.9387589250914</v>
+        <v>-36.6676652375296</v>
       </c>
       <c r="E12" t="n">
-        <v>0.62198898147019</v>
+        <v>-0.844086804346954</v>
       </c>
       <c r="F12" t="n">
-        <v>0.544703868905332</v>
+        <v>0.41388440923493</v>
       </c>
       <c r="G12" t="n">
-        <v>0.662899475860843</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>22.0145340190966</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.517225465350585</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.613686061860048</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.662899475860843</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>51.6419511014861</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.04378094637138</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.31560867614285</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.662899475860843</v>
+        <v>0.779723152054572</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +1908,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2153,21 +1917,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>12.0117085878997</v>
+        <v>5.02494550931344</v>
       </c>
       <c r="E2" t="n">
-        <v>0.951489834833324</v>
+        <v>0.456924333846464</v>
       </c>
       <c r="F2" t="n">
-        <v>0.360127761942322</v>
+        <v>0.655886391270426</v>
       </c>
       <c r="G2" t="n">
-        <v>0.763377686022287</v>
+        <v>0.815460422187623</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2176,21 +1940,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.314751817897638</v>
+        <v>-15.6693791447019</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0328798279334025</v>
+        <v>-1.58697919645307</v>
       </c>
       <c r="F3" t="n">
-        <v>0.974310986973964</v>
+        <v>0.138502694066731</v>
       </c>
       <c r="G3" t="n">
-        <v>0.974310986973964</v>
+        <v>0.815460422187623</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2199,21 +1963,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>8.3860253429882</v>
+        <v>-2.23418282698048</v>
       </c>
       <c r="E4" t="n">
-        <v>0.929678139389936</v>
+        <v>-0.233444128872382</v>
       </c>
       <c r="F4" t="n">
-        <v>0.370862409604832</v>
+        <v>0.819351293381484</v>
       </c>
       <c r="G4" t="n">
-        <v>0.763377686022287</v>
+        <v>0.896787243167155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2222,21 +1986,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-17.2642348370799</v>
+        <v>5.82233929475659</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5830950581715</v>
+        <v>0.573139087252035</v>
       </c>
       <c r="F5" t="n">
-        <v>0.139384924235485</v>
+        <v>0.577133115762269</v>
       </c>
       <c r="G5" t="n">
-        <v>0.763377686022287</v>
+        <v>0.815460422187623</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2245,21 +2009,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>8.10776723815438</v>
+        <v>6.7731690319771</v>
       </c>
       <c r="E6" t="n">
-        <v>0.760051724729119</v>
+        <v>0.629299874188261</v>
       </c>
       <c r="F6" t="n">
-        <v>0.461895771161084</v>
+        <v>0.540948361105774</v>
       </c>
       <c r="G6" t="n">
-        <v>0.763377686022287</v>
+        <v>0.815460422187623</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2268,21 +2032,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>11.9992326635375</v>
+        <v>12.1758922055486</v>
       </c>
       <c r="E7" t="n">
-        <v>0.997782464261929</v>
+        <v>0.958344862683201</v>
       </c>
       <c r="F7" t="n">
-        <v>0.338080158228424</v>
+        <v>0.356799931400322</v>
       </c>
       <c r="G7" t="n">
-        <v>0.763377686022287</v>
+        <v>0.815460422187623</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2291,21 +2055,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>1.98430463452959</v>
+        <v>4.92744495330898</v>
       </c>
       <c r="E8" t="n">
-        <v>0.18495752681189</v>
+        <v>0.520453723543173</v>
       </c>
       <c r="F8" t="n">
-        <v>0.856351513731592</v>
+        <v>0.612215284171165</v>
       </c>
       <c r="G8" t="n">
-        <v>0.974310986973964</v>
+        <v>0.815460422187623</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2314,21 +2078,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>7.55811432422725</v>
+        <v>-5.28544916658943</v>
       </c>
       <c r="E9" t="n">
-        <v>0.746444529565671</v>
+        <v>-0.440799004146816</v>
       </c>
       <c r="F9" t="n">
-        <v>0.469770883706023</v>
+        <v>0.667194890880783</v>
       </c>
       <c r="G9" t="n">
-        <v>0.763377686022287</v>
+        <v>0.815460422187623</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2337,21 +2101,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>4.57407762198319</v>
+        <v>-9.57153442376761</v>
       </c>
       <c r="E10" t="n">
-        <v>0.435108504058856</v>
+        <v>-0.850900586392307</v>
       </c>
       <c r="F10" t="n">
-        <v>0.671206226513786</v>
+        <v>0.41148236806757</v>
       </c>
       <c r="G10" t="n">
-        <v>0.872568094467922</v>
+        <v>0.815460422187623</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2360,21 +2124,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.5951999480468</v>
+        <v>-1.24941650597977</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.59395371507322</v>
+        <v>-0.132496674381245</v>
       </c>
       <c r="F11" t="n">
-        <v>0.136930700840661</v>
+        <v>0.896787243167155</v>
       </c>
       <c r="G11" t="n">
-        <v>0.763377686022287</v>
+        <v>0.896787243167155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2383,62 +2147,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.42011988340662</v>
+        <v>8.94426694546715</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.552117501814945</v>
+        <v>0.972470688629342</v>
       </c>
       <c r="F12" t="n">
-        <v>0.591002650951783</v>
+        <v>0.350011566026064</v>
       </c>
       <c r="G12" t="n">
-        <v>0.853670495819242</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.971139525567709</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.102774619905211</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.919839371269628</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.974310986973964</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-11.3937286076768</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.08103334862749</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.300929251962694</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.763377686022287</v>
+        <v>0.815460422187623</v>
       </c>
     </row>
   </sheetData>
@@ -2454,71 +2172,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>13.0627200078071</v>
+        <v>17.7718488826961</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2527,24 +2245,24 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>8.10776723815438</v>
+        <v>5.82233929475659</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2553,24 +2271,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>36.8458058819689</v>
+        <v>36.6676652375296</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2579,24 +2297,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1728.85729581191</v>
+        <v>1789.85514091352</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2605,33 +2323,33 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1553.89321443555</v>
+        <v>1620.70298921829</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.05296457953113</v>
+        <v>2.55496905702803</v>
       </c>
     </row>
   </sheetData>
